--- a/public/templates/planilla_proyectado_modelo.xlsx
+++ b/public/templates/planilla_proyectado_modelo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tierrasanta\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9CCD45-D965-4BD0-A129-47C834F6710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864147A9-60E4-45C9-9A53-08894E01D634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{0D0853FD-6A20-4A77-9B43-493267389889}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{0D0853FD-6A20-4A77-9B43-493267389889}"/>
   </bookViews>
   <sheets>
     <sheet name="PROYECTADA" sheetId="4" r:id="rId1"/>
@@ -5892,6 +5892,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7587,11 +7588,44 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7616,39 +7650,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8404,55 +8405,55 @@
         <v>98</v>
       </c>
       <c r="U3" s="30"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
-      <c r="AA3" s="265"/>
-      <c r="AB3" s="265"/>
-      <c r="AC3" s="265"/>
-      <c r="AD3" s="265"/>
+      <c r="X3" s="277"/>
+      <c r="Y3" s="277"/>
+      <c r="Z3" s="277"/>
+      <c r="AA3" s="277"/>
+      <c r="AB3" s="277"/>
+      <c r="AC3" s="277"/>
+      <c r="AD3" s="277"/>
       <c r="AE3" s="32"/>
-      <c r="AF3" s="265" t="s">
+      <c r="AF3" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="AG3" s="265"/>
-      <c r="AH3" s="265"/>
-      <c r="AI3" s="265"/>
+      <c r="AG3" s="277"/>
+      <c r="AH3" s="277"/>
+      <c r="AI3" s="277"/>
     </row>
     <row r="4" spans="1:35" ht="20.399999999999999" customHeight="1">
-      <c r="A4" s="273" t="s">
+      <c r="A4" s="284" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
-      <c r="L4" s="274"/>
-      <c r="M4" s="274"/>
-      <c r="N4" s="274"/>
-      <c r="O4" s="274"/>
-      <c r="P4" s="274"/>
-      <c r="Q4" s="274"/>
-      <c r="R4" s="274"/>
-      <c r="S4" s="274"/>
-      <c r="T4" s="274"/>
-      <c r="U4" s="274"/>
-      <c r="V4" s="274"/>
-      <c r="X4" s="265" t="s">
+      <c r="B4" s="285"/>
+      <c r="C4" s="285"/>
+      <c r="D4" s="285"/>
+      <c r="E4" s="285"/>
+      <c r="F4" s="285"/>
+      <c r="G4" s="285"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="285"/>
+      <c r="L4" s="285"/>
+      <c r="M4" s="285"/>
+      <c r="N4" s="285"/>
+      <c r="O4" s="285"/>
+      <c r="P4" s="285"/>
+      <c r="Q4" s="285"/>
+      <c r="R4" s="285"/>
+      <c r="S4" s="285"/>
+      <c r="T4" s="285"/>
+      <c r="U4" s="285"/>
+      <c r="V4" s="285"/>
+      <c r="X4" s="277" t="s">
         <v>3</v>
       </c>
-      <c r="Y4" s="265"/>
-      <c r="Z4" s="265"/>
-      <c r="AA4" s="265"/>
-      <c r="AB4" s="265"/>
-      <c r="AC4" s="265"/>
-      <c r="AD4" s="265"/>
+      <c r="Y4" s="277"/>
+      <c r="Z4" s="277"/>
+      <c r="AA4" s="277"/>
+      <c r="AB4" s="277"/>
+      <c r="AC4" s="277"/>
+      <c r="AD4" s="277"/>
       <c r="AE4" s="32"/>
       <c r="AF4" s="31"/>
       <c r="AG4" s="31"/>
@@ -8460,87 +8461,87 @@
       <c r="AI4" s="31"/>
     </row>
     <row r="5" spans="1:35" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="281" t="s">
+      <c r="A5" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="281" t="s">
+      <c r="B5" s="266" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="280" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="279" t="s">
+      <c r="C5" s="276" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="275" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="279"/>
-      <c r="F5" s="279"/>
-      <c r="G5" s="279"/>
-      <c r="H5" s="266" t="s">
+      <c r="E5" s="275"/>
+      <c r="F5" s="275"/>
+      <c r="G5" s="275"/>
+      <c r="H5" s="274" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="266" t="s">
+      <c r="I5" s="274" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="268" t="s">
+      <c r="J5" s="279" t="s">
         <v>93</v>
       </c>
-      <c r="K5" s="271" t="s">
+      <c r="K5" s="282" t="s">
         <v>99</v>
       </c>
-      <c r="L5" s="271"/>
-      <c r="M5" s="271"/>
-      <c r="N5" s="271"/>
-      <c r="O5" s="272" t="s">
+      <c r="L5" s="282"/>
+      <c r="M5" s="282"/>
+      <c r="N5" s="282"/>
+      <c r="O5" s="283" t="s">
         <v>102</v>
       </c>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="285" t="s">
+      <c r="P5" s="283"/>
+      <c r="Q5" s="283"/>
+      <c r="R5" s="283"/>
+      <c r="S5" s="270" t="s">
         <v>100</v>
       </c>
-      <c r="T5" s="284" t="s">
+      <c r="T5" s="269" t="s">
         <v>101</v>
       </c>
-      <c r="U5" s="283" t="s">
+      <c r="U5" s="268" t="s">
         <v>17</v>
       </c>
-      <c r="V5" s="282" t="s">
+      <c r="V5" s="267" t="s">
         <v>18</v>
       </c>
       <c r="W5" s="35"/>
-      <c r="X5" s="267" t="s">
+      <c r="X5" s="278" t="s">
         <v>6</v>
       </c>
-      <c r="Y5" s="267" t="s">
+      <c r="Y5" s="278" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="275" t="s">
+      <c r="Z5" s="265" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="275" t="s">
+      <c r="AA5" s="265" t="s">
         <v>20</v>
       </c>
-      <c r="AB5" s="275" t="s">
+      <c r="AB5" s="265" t="s">
         <v>21</v>
       </c>
-      <c r="AC5" s="275" t="s">
+      <c r="AC5" s="265" t="s">
         <v>22</v>
       </c>
-      <c r="AD5" s="275" t="s">
+      <c r="AD5" s="265" t="s">
         <v>23</v>
       </c>
-      <c r="AF5" s="269" t="s">
+      <c r="AF5" s="280" t="s">
         <v>24</v>
       </c>
-      <c r="AG5" s="270" t="s">
+      <c r="AG5" s="281" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="39.6" customHeight="1">
-      <c r="A6" s="281"/>
-      <c r="B6" s="281"/>
-      <c r="C6" s="280"/>
+      <c r="A6" s="266"/>
+      <c r="B6" s="266"/>
+      <c r="C6" s="276"/>
       <c r="D6" s="36" t="s">
         <v>9</v>
       </c>
@@ -8553,9 +8554,9 @@
       <c r="G6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
-      <c r="J6" s="268"/>
+      <c r="H6" s="274"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="279"/>
       <c r="K6" s="33" t="s">
         <v>13</v>
       </c>
@@ -8580,20 +8581,20 @@
       <c r="R6" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="S6" s="285"/>
-      <c r="T6" s="284"/>
-      <c r="U6" s="283"/>
-      <c r="V6" s="282"/>
+      <c r="S6" s="270"/>
+      <c r="T6" s="269"/>
+      <c r="U6" s="268"/>
+      <c r="V6" s="267"/>
       <c r="W6" s="40"/>
-      <c r="X6" s="267"/>
-      <c r="Y6" s="267"/>
-      <c r="Z6" s="275"/>
-      <c r="AA6" s="275"/>
-      <c r="AB6" s="275"/>
-      <c r="AC6" s="275"/>
-      <c r="AD6" s="275"/>
-      <c r="AF6" s="269"/>
-      <c r="AG6" s="270"/>
+      <c r="X6" s="278"/>
+      <c r="Y6" s="278"/>
+      <c r="Z6" s="265"/>
+      <c r="AA6" s="265"/>
+      <c r="AB6" s="265"/>
+      <c r="AC6" s="265"/>
+      <c r="AD6" s="265"/>
+      <c r="AF6" s="280"/>
+      <c r="AG6" s="281"/>
       <c r="AI6" s="41" t="s">
         <v>26</v>
       </c>
@@ -14388,11 +14389,11 @@
       <c r="Z61" s="7"/>
     </row>
     <row r="62" spans="1:35" ht="14.4" thickBot="1">
-      <c r="C62" s="276" t="s">
+      <c r="C62" s="271" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="277"/>
-      <c r="E62" s="278"/>
+      <c r="D62" s="272"/>
+      <c r="E62" s="273"/>
       <c r="F62" s="11"/>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
@@ -14648,17 +14649,6 @@
     <filterColumn colId="16" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="AF3:AI3"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="X5:X6"/>
@@ -14675,6 +14665,17 @@
     <mergeCell ref="AC5:AC6"/>
     <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14853,36 +14854,36 @@
       </c>
     </row>
     <row r="4" spans="1:50" ht="20.399999999999999" customHeight="1">
-      <c r="A4" s="273" t="s">
+      <c r="A4" s="284" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
-      <c r="L4" s="274"/>
-      <c r="M4" s="274"/>
-      <c r="N4" s="274"/>
-      <c r="O4" s="274"/>
-      <c r="P4" s="274"/>
-      <c r="Q4" s="274"/>
-      <c r="R4" s="274"/>
-      <c r="S4" s="274"/>
-      <c r="T4" s="274"/>
-      <c r="U4" s="274"/>
-      <c r="V4" s="274"/>
-      <c r="W4" s="274"/>
-      <c r="X4" s="274"/>
-      <c r="Y4" s="274"/>
-      <c r="Z4" s="274"/>
-      <c r="AA4" s="274"/>
-      <c r="AB4" s="274"/>
+      <c r="B4" s="285"/>
+      <c r="C4" s="285"/>
+      <c r="D4" s="285"/>
+      <c r="E4" s="285"/>
+      <c r="F4" s="285"/>
+      <c r="G4" s="285"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="285"/>
+      <c r="L4" s="285"/>
+      <c r="M4" s="285"/>
+      <c r="N4" s="285"/>
+      <c r="O4" s="285"/>
+      <c r="P4" s="285"/>
+      <c r="Q4" s="285"/>
+      <c r="R4" s="285"/>
+      <c r="S4" s="285"/>
+      <c r="T4" s="285"/>
+      <c r="U4" s="285"/>
+      <c r="V4" s="285"/>
+      <c r="W4" s="285"/>
+      <c r="X4" s="285"/>
+      <c r="Y4" s="285"/>
+      <c r="Z4" s="285"/>
+      <c r="AA4" s="285"/>
+      <c r="AB4" s="285"/>
       <c r="AC4" s="183"/>
       <c r="AD4" s="183"/>
       <c r="AE4" s="183"/>
